--- a/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Identity Source Configuration / Source Configuration for Employee Management</t>
+          <t>Employee Source Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Candidate Source Configuration / Source Configuration for Candidate Management</t>
+          <t>Candidate Source Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Time Based Settings / Timezone Configuration</t>
+          <t>Time Based Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attribute Cache / Can be moved to Source Configuration section?</t>
+          <t>Attribute Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PII Attributes / Can be moved under policy</t>
+          <t>Define PII Attributes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mailbox Settings</t>
+          <t>Directory Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,85 +781,85 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OneDrive Settings</t>
+          <t>Target Application Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Device Settings</t>
+          <t>Synchronization Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
+          <t>01KMJ2YB1Y0Z8SCBTW9S8E97MF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJ2YB1Y0Z8SCBTW9S8E97MF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Groups Settings</t>
+          <t>Target Directory Assignment Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+          <t>01KMJ30VKYKZT7E5R2FZBFY2WS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJ30VKYKZT7E5R2FZBFY2WS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WriteBack Settings / Writeback Settings</t>
+          <t>Manage Employee - AD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,164 +869,956 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>01KMJFJ7EWSXBG3MC60VXC8Q7M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFJ7EWSXBG3MC60VXC8Q7M</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Identity Mapping</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>01KMJFKP2NXMBY17A86HZQB5WE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFKP2NXMBY17A86HZQB5WE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Account Creation Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>01KMJFSHD2M8QJ6FNTKAYQEPBW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7V436R8NAB6DY1Q9CZ0K6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFSHD2M8QJ6FNTKAYQEPBW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Account Update Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>01KMM530DPFP25CT8P12W5ZV79</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7VBW5CRXEP8KGFHBYG161</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM530DPFP25CT8P12W5ZV79</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Account Deactivation Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>01KMM54TDXMGNMGSRG62JYPN5K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM54TDXMGNMGSRG62JYPN5K</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMQ7VRVT1E4AD0BFY20V8496</t>
+          <t>h_01KMM5A8XS2FT0AYY8DG5BD024</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7VRVT1E4AD0BFY20V8496</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMM5A8XS2FT0AYY8DG5BD024</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Manage Candidate - AD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+          <t>01KMM89QASD6PVCPJMESF136AA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASD6PVCPJMESF136AA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Account Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>01KMM89QASTXKNWG9C54PNXZCP</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASTXKNWG9C54PNXZCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Account Activation Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>01KMM89QASYY5QYFG4YVPNMBZ4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASYY5QYFG4YVPNMBZ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>01KMM9JSKN5QKPTEMV6G98J7X4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9JSKN5QKPTEMV6G98J7X4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Account Deactivation Settings</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>01KMM9TW3ERRSQTDZ0AAG52KDG</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9TW3ERRSQTDZ0AAG52KDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>01KMM9Z8S3RFW84RB6A0JEKASR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9Z8S3RFW84RB6A0JEKASR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Manage Employee - Entra ID</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>01KMPR5X84XTP5K0RP94BV50SF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPR5X84XTP5K0RP94BV50SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Account Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>01KMPRJJS6VTJ0E3W02S22DTPF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6VTJ0E3W02S22DTPF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Account Activation Settings</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>01KMPRJJS6Y9GQ0Q5SKP21S97C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6Y9GQ0Q5SKP21S97C</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>01KMPRJJS6F1ZM4VXJE7T1D6X8</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6F1ZM4VXJE7T1D6X8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Account Deactivation Settings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>01KMPRJJS696C6889SSCVBANZE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS696C6889SSCVBANZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>01KMPRJJS6QPVWDR13Q9VX3GJN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6QPVWDR13Q9VX3GJN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Manage Candidate - Entra ID</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>01KMPR4HH49Y6PR2WW8RW99BSG</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPR4HH49Y6PR2WW8RW99BSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Account Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>01KN3RB5W0F2ZDP8H86TD5EMVD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W0F2ZDP8H86TD5EMVD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Account Activation Settings</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>01KN3RB5W0493K9CFA276MJCVH</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W0493K9CFA276MJCVH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Account Update Settings</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>01KN3RB5W01RB1DJPFZD927HY3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W01RB1DJPFZD927HY3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Account Deactivation Settings</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>01KN3RB5W1Q9RZ616HT2QM6ZNP</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W1Q9RZ616HT2QM6ZNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Attribute Mapping</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>01KN3RB5W1NVZ4E6DHY20MBFVY</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W1NVZ4E6DHY20MBFVY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mailbox Settings</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OneDrive Settings</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Device Settings</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Groups Settings</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WriteBack Settings</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Advance Settings</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Operational Settings Definition</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Template Library</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Provisioning Methods</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
         </is>

--- a/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Supported Provisioning Methods</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,63 +495,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01KMM9BYN5GDF0VKSZEQZD3XVQ</t>
+          <t>h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMM9BYN5GDF0VKSZEQZD3XVQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01KMM9BYN5GDF0VKSZEQZD3XVQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMM9BYN5GDF0VKSZEQZD3XVQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,107 +561,107 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features List</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
+          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Features List</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMMA69K704VGB3TJEGRDBT26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KMQ7T44VZFB5PBARG0TYREKF</t>
+          <t>h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7T44VZFB5PBARG0TYREKF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KFZGBB1GN0RB6E0SP3SYR0BS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Employee Source Configuration</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KMQ8T0H858Q6EASJRRVCJA22</t>
+          <t>h_01KMQ7T44VZFB5PBARG0TYREKF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ8T0H858Q6EASJRRVCJA22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7T44VZFB5PBARG0TYREKF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Candidate Source Configuration</t>
+          <t>Employee Source Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KMQNGJCFQZN9JT6F2P6Z0TBM</t>
+          <t>h_01KMQ8T0H858Q6EASJRRVCJA22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNGJCFQZN9JT6F2P6Z0TBM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ8T0H858Q6EASJRRVCJA22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Time Based Settings</t>
+          <t>Candidate Source Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KMZHBBGFSRX4RBMD3WW86DCN</t>
+          <t>h_01KMQNGJCFQZN9JT6F2P6Z0TBM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZHBBGFSRX4RBMD3WW86DCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNGJCFQZN9JT6F2P6Z0TBM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attribute Settings</t>
+          <t>Time Based Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMZHBBGG0RGHQ04VVAP3J6RJ</t>
+          <t>h_01KMZHBBGFSRX4RBMD3WW86DCN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZHBBGG0RGHQ04VVAP3J6RJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZHBBGFSRX4RBMD3WW86DCN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Define PII Attributes</t>
+          <t>Attribute Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,85 +737,85 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMZHBBGG9D8BERBETDSS9G8J</t>
+          <t>h_01KMZHBBGG0RGHQ04VVAP3J6RJ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZHBBGG9D8BERBETDSS9G8J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZHBBGG0RGHQ04VVAP3J6RJ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Define PII Attributes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
+          <t>h_01KMZHBBGG9D8BERBETDSS9G8J</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZHBBGG9D8BERBETDSS9G8J</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Directory Settings</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ95W0VKEWZT0G3MVJZ0SR8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Target Application Configuration</t>
+          <t>Directory Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Synchronization Settings</t>
+          <t>Target Application Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KMJ2YB1Y0Z8SCBTW9S8E97MF</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJ2YB1Y0Z8SCBTW9S8E97MF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Target Directory Assignment Settings</t>
+          <t>Synchronization Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KMJ30VKYKZT7E5R2FZBFY2WS</t>
+          <t>01KMJ2YB1Y0Z8SCBTW9S8E97MF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJ30VKYKZT7E5R2FZBFY2WS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJ2YB1Y0Z8SCBTW9S8E97MF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manage Employee - AD</t>
+          <t>Target Directory Assignment Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KMJFJ7EWSXBG3MC60VXC8Q7M</t>
+          <t>01KMJ30VKYKZT7E5R2FZBFY2WS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFJ7EWSXBG3MC60VXC8Q7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJ30VKYKZT7E5R2FZBFY2WS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Identity Mapping</t>
+          <t>Manage Employee - AD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KMJFKP2NXMBY17A86HZQB5WE</t>
+          <t>01KMJFJ7EWSXBG3MC60VXC8Q7M</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFKP2NXMBY17A86HZQB5WE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFJ7EWSXBG3MC60VXC8Q7M</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Account Creation Settings</t>
+          <t>Identity Mapping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KMJFSHD2M8QJ6FNTKAYQEPBW</t>
+          <t>01KMJFKP2NXMBY17A86HZQB5WE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFSHD2M8QJ6FNTKAYQEPBW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFKP2NXMBY17A86HZQB5WE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Account Update Settings</t>
+          <t>Account Creation Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01KMM530DPFP25CT8P12W5ZV79</t>
+          <t>01KMJFSHD2M8QJ6FNTKAYQEPBW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM530DPFP25CT8P12W5ZV79</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMJFSHD2M8QJ6FNTKAYQEPBW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Account Deactivation Settings</t>
+          <t>Account Update Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KMM54TDXMGNMGSRG62JYPN5K</t>
+          <t>01KMM530DPFP25CT8P12W5ZV79</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM54TDXMGNMGSRG62JYPN5K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM530DPFP25CT8P12W5ZV79</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Account Deactivation Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,63 +979,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMM5A8XS2FT0AYY8DG5BD024</t>
+          <t>01KMM54TDXMGNMGSRG62JYPN5K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMM5A8XS2FT0AYY8DG5BD024</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM54TDXMGNMGSRG62JYPN5K</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Manage Candidate - AD</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KMM89QASD6PVCPJMESF136AA</t>
+          <t>h_01KMM5A8XS2FT0AYY8DG5BD024</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASD6PVCPJMESF136AA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMM5A8XS2FT0AYY8DG5BD024</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Account Correlation Settings</t>
+          <t>Manage Candidate - AD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KMM89QASTXKNWG9C54PNXZCP</t>
+          <t>01KMM89QASD6PVCPJMESF136AA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASTXKNWG9C54PNXZCP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASD6PVCPJMESF136AA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Account Activation Settings</t>
+          <t>Account Correlation Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KMM89QASYY5QYFG4YVPNMBZ4</t>
+          <t>01KMM89QASTXKNWG9C54PNXZCP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASYY5QYFG4YVPNMBZ4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASTXKNWG9C54PNXZCP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Account Update Settings</t>
+          <t>Account Activation Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01KMM9JSKN5QKPTEMV6G98J7X4</t>
+          <t>01KMM89QASYY5QYFG4YVPNMBZ4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9JSKN5QKPTEMV6G98J7X4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM89QASYY5QYFG4YVPNMBZ4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Account Deactivation Settings</t>
+          <t>Account Update Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01KMM9TW3ERRSQTDZ0AAG52KDG</t>
+          <t>01KMM9JSKN5QKPTEMV6G98J7X4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9TW3ERRSQTDZ0AAG52KDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9JSKN5QKPTEMV6G98J7X4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Account Deactivation Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,63 +1111,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01KMM9Z8S3RFW84RB6A0JEKASR</t>
+          <t>01KMM9TW3ERRSQTDZ0AAG52KDG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9Z8S3RFW84RB6A0JEKASR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9TW3ERRSQTDZ0AAG52KDG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Manage Employee - Entra ID</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01KMPR5X84XTP5K0RP94BV50SF</t>
+          <t>01KMM9Z8S3RFW84RB6A0JEKASR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPR5X84XTP5K0RP94BV50SF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMM9Z8S3RFW84RB6A0JEKASR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Account Correlation Settings</t>
+          <t>Manage Employee - Entra ID</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01KMPRJJS6VTJ0E3W02S22DTPF</t>
+          <t>01KMPR5X84XTP5K0RP94BV50SF</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6VTJ0E3W02S22DTPF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPR5X84XTP5K0RP94BV50SF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Account Activation Settings</t>
+          <t>Account Correlation Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01KMPRJJS6Y9GQ0Q5SKP21S97C</t>
+          <t>01KMPRJJS6VTJ0E3W02S22DTPF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6Y9GQ0Q5SKP21S97C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6VTJ0E3W02S22DTPF</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Account Update Settings</t>
+          <t>Account Activation Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01KMPRJJS6F1ZM4VXJE7T1D6X8</t>
+          <t>01KMPRJJS6Y9GQ0Q5SKP21S97C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6F1ZM4VXJE7T1D6X8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6Y9GQ0Q5SKP21S97C</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Account Deactivation Settings</t>
+          <t>Account Update Settings</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01KMPRJJS696C6889SSCVBANZE</t>
+          <t>01KMPRJJS6F1ZM4VXJE7T1D6X8</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS696C6889SSCVBANZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6F1ZM4VXJE7T1D6X8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Account Deactivation Settings</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,63 +1243,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01KMPRJJS6QPVWDR13Q9VX3GJN</t>
+          <t>01KMPRJJS696C6889SSCVBANZE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6QPVWDR13Q9VX3GJN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS696C6889SSCVBANZE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Manage Candidate - Entra ID</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01KMPR4HH49Y6PR2WW8RW99BSG</t>
+          <t>01KMPRJJS6QPVWDR13Q9VX3GJN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPR4HH49Y6PR2WW8RW99BSG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPRJJS6QPVWDR13Q9VX3GJN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Account Correlation Settings</t>
+          <t>Manage Candidate - Entra ID</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01KN3RB5W0F2ZDP8H86TD5EMVD</t>
+          <t>01KMPR4HH49Y6PR2WW8RW99BSG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W0F2ZDP8H86TD5EMVD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KMPR4HH49Y6PR2WW8RW99BSG</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Account Activation Settings</t>
+          <t>Account Correlation Settings</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01KN3RB5W0493K9CFA276MJCVH</t>
+          <t>01KN3RB5W0F2ZDP8H86TD5EMVD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W0493K9CFA276MJCVH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W0F2ZDP8H86TD5EMVD</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Account Update Settings</t>
+          <t>Account Activation Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,19 +1331,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01KN3RB5W01RB1DJPFZD927HY3</t>
+          <t>01KN3RB5W0493K9CFA276MJCVH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W01RB1DJPFZD927HY3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W0493K9CFA276MJCVH</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Account Deactivation Settings</t>
+          <t>Account Update Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01KN3RB5W1Q9RZ616HT2QM6ZNP</t>
+          <t>01KN3RB5W01RB1DJPFZD927HY3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W1Q9RZ616HT2QM6ZNP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W01RB1DJPFZD927HY3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Account Deactivation Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,41 +1375,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01KN3RB5W1NVZ4E6DHY20MBFVY</t>
+          <t>01KN3RB5W1Q9RZ616HT2QM6ZNP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W1NVZ4E6DHY20MBFVY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W1Q9RZ616HT2QM6ZNP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mailbox Settings</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+          <t>01KN3RB5W1NVZ4E6DHY20MBFVY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBK83XCVZZF3RY26PJXS2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#01KN3RB5W1NVZ4E6DHY20MBFVY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OneDrive Settings</t>
+          <t>Mailbox Settings</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,19 +1419,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+          <t>h_01KN1TBK83XCVZZF3RY26PJXS2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBK83XCVZZF3RY26PJXS2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Device Settings</t>
+          <t>OneDrive Settings</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
+          <t>h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TBZY5Q4C9AN1ZHRDMXAHP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Groups Settings</t>
+          <t>Device Settings</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+          <t>h_01KN1TCB7YSSTH14250DTZDD4F</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCB7YSSTH14250DTZDD4F</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WriteBack Settings</t>
+          <t>Groups Settings</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,41 +1485,41 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1TCKBWQRHN1ZKMW2Z7BQM6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>WriteBack Settings</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMZG877J1FGTK7QZB1DV7H2R</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,41 +1529,41 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+          <t>h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7TX7BWSQ5G56YKZ7PKWND</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,85 +1573,85 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operational Settings Definition</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Operational Settings Definition</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Template Library</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Template Library</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1683,41 +1683,41 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,41 +1727,41 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,19 +1771,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,34 +1793,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01KN42W8X60FH5MKJE4RYF9CGN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN42W8X60FH5MKJE4RYF9CGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Provisioning Methods</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3VWFN63Z6QM0B9AGMBP9JY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,29 +1541,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Business Groups</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Access Rules</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,41 +1573,41 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KKKEZG6H87DM8VPRD0V2Q9NW</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Organizational Unit (OU) Assignment Rules</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>h_01KMN29FF651PEW913V0D17KT4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN29FF651PEW913V0D17KT4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Operational Settings Definition</t>
+          <t>Organisation Unit Employee (OU)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,85 +1617,85 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+          <t>h_01KMQBXYNJ6DC2BYP73FRMAZAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQBXYNJ6DC2BYP73FRMAZAN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Monitoring Rules</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+          <t>h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNB8YF19XTGQXY5SNGKXZJ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Monitoring Settings</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ23A5EVANCP3A0G0VFMZS6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Template Library</t>
+          <t>Rule Detail (Monitoring)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ23Z6WK14YVW1GGJ9GETMZ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,98 +1705,406 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KMN40VMF41N5TF8FPZDF6A53</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN40VMF41N5TF8FPZDF6A53</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Naming Policy Settings</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KMN45XQR7V20BD6R5JVQMJ92</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN45XQR7V20BD6R5JVQMJ92</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Generate sAMAccountName</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KMN4GEKY0M4KPDGR1EJ3FCH8</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN4GEKY0M4KPDGR1EJ3FCH8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Generate UserPrincipalName (UPN)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KMN5EYC0AQNMA7FKB80GCRM2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC0AQNMA7FKB80GCRM2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Generate Email</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>h_01KMN5EYC063KGS56YDE8Z6ATT</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC063KGS56YDE8Z6ATT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Generate Common Name (CN)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>h_01KMN5EYC0JTZT4ZY8TTQ7KCX9</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMN5EYC0JTZT4ZY8TTQ7KCX9</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>h_01KMQNB8YFJHAQHKRTEZ19XQQE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQNB8YFJHAQHKRTEZ19XQQE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1VKJFQ9FAWC8B6EY7ECH5N</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Advance Settings</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Operational Settings Definition</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1ASDTRY0GR0850VZCFF8FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Template Library</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Active-Directory-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
